--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.67556628306622</v>
+        <v>10.50977952099826</v>
       </c>
       <c r="D2" t="n">
-        <v>20.74514668810783</v>
+        <v>3.371086336817522</v>
       </c>
       <c r="E2" t="n">
-        <v>10.16227011185022</v>
+        <v>1.651368893175662</v>
       </c>
       <c r="F2" t="n">
-        <v>6.637031575889329</v>
+        <v>1.078517631082016</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.70361136142102</v>
+        <v>6.451836846230916</v>
       </c>
       <c r="D3" t="n">
-        <v>38.45614546007329</v>
+        <v>6.249123637261911</v>
       </c>
       <c r="E3" t="n">
-        <v>10.16227011185022</v>
+        <v>1.651368893175662</v>
       </c>
       <c r="F3" t="n">
-        <v>6.637031575889329</v>
+        <v>1.078517631082016</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.4603084212641</v>
+        <v>10.47480011845542</v>
       </c>
       <c r="D4" t="n">
-        <v>29.25277013647761</v>
+        <v>4.753575147177613</v>
       </c>
       <c r="E4" t="n">
-        <v>10.16227011185022</v>
+        <v>1.651368893175662</v>
       </c>
       <c r="F4" t="n">
-        <v>6.637031575889329</v>
+        <v>1.078517631082016</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.17995232263033</v>
+        <v>8.966742252427428</v>
       </c>
       <c r="D5" t="n">
-        <v>24.41446910789537</v>
+        <v>3.967351230032998</v>
       </c>
       <c r="E5" t="n">
-        <v>10.16227011185022</v>
+        <v>1.651368893175662</v>
       </c>
       <c r="F5" t="n">
-        <v>6.637031575889329</v>
+        <v>1.078517631082016</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
